--- a/Results/- Full Results.xlsx
+++ b/Results/- Full Results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26924"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Google Drive\Github\Evaluation-of-Perceptual-Hash-Algorithms\Results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4927843D-8C71-4727-9BE0-080E33310B7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52913688-33FE-40AA-9078-AFF91327FACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="4" xr2:uid="{8ECD64AB-BFC1-4230-991D-53B694B4B77A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{8ECD64AB-BFC1-4230-991D-53B694B4B77A}"/>
   </bookViews>
   <sheets>
     <sheet name="LennaDatabase" sheetId="9" r:id="rId1"/>
@@ -522,14 +522,17 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="pt-BR" b="1"/>
-              <a:t>Distância de Hamming para Cada Algoritmo de Hashing entre a Imagem Original e uma Imagem Alterada</a:t>
+              <a:rPr lang="pt-BR" b="1">
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:rPr>
+              <a:t>Distância de Hamming - Lenna Database</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -550,10 +553,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="6.708286735947222E-2"/>
+          <c:x val="8.2984159333859636E-2"/>
           <c:y val="9.442161516380955E-2"/>
-          <c:w val="0.92001075377594732"/>
-          <c:h val="0.60924529054121401"/>
+          <c:w val="0.9041095215780599"/>
+          <c:h val="0.52956826499817333"/>
         </c:manualLayout>
       </c:layout>
       <c:lineChart>
@@ -1220,6 +1223,121 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000003-955C-4A62-A711-ABC0A9DA8470}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="10"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>LennaDatabase!#REF!</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>#REF!</c:v>
+                </c:pt>
+              </c:strCache>
+              <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
+            </c:strRef>
+          </c:tx>
+          <c:marker>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>LennaDatabase!$A$2:$A$21</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>LennaDatabase!$A$3:$A$21</c:f>
+              <c:strCache>
+                <c:ptCount val="19"/>
+                <c:pt idx="0">
+                  <c:v>Imagem Original</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Imagem em Bmp</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Imagem em Png</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Imagem em Tiff</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Gaussiana 3x3</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Gaussiana 7x7</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Mediana 7x7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>Mediana 3x3</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>Média 3x3</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>Média 7x7</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>Pouca alteração</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>Adição de Texto</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>Escala de Cinza</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>Ruído Sal e Pimenta</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>Bordas Enfatizadas</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>Muita alteração</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>Binarização com OTSU</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>Metade Alterada</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>Efeito Espelho</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>Adição de Objetos</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>LennaDatabase!#REF!</c:f>
+              <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-955C-4A62-A711-ABC0A9DA8470}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1420,143 +1538,7 @@
         <c:smooth val="0"/>
         <c:axId val="392150687"/>
         <c:axId val="392152351"/>
-        <c:extLst>
-          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-            <c15:filteredLineSeries>
-              <c15:ser>
-                <c:idx val="10"/>
-                <c:order val="4"/>
-                <c:tx>
-                  <c:strRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>LennaDatabase!#REF!</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:strCache>
-                      <c:ptCount val="1"/>
-                      <c:pt idx="0">
-                        <c:v>#REF!</c:v>
-                      </c:pt>
-                    </c:strCache>
-                  </c:strRef>
-                </c:tx>
-                <c:marker>
-                  <c:spPr>
-                    <a:solidFill>
-                      <a:schemeClr val="accent6"/>
-                    </a:solidFill>
-                    <a:ln>
-                      <a:solidFill>
-                        <a:schemeClr val="accent6"/>
-                      </a:solidFill>
-                    </a:ln>
-                  </c:spPr>
-                </c:marker>
-                <c:cat>
-                  <c:strRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:fullRef>
-                          <c15:sqref>LennaDatabase!$A$2:$A$21</c15:sqref>
-                        </c15:fullRef>
-                        <c15:formulaRef>
-                          <c15:sqref>LennaDatabase!$A$3:$A$21</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:strCache>
-                      <c:ptCount val="19"/>
-                      <c:pt idx="0">
-                        <c:v>Imagem em Bmp</c:v>
-                      </c:pt>
-                      <c:pt idx="1">
-                        <c:v>Imagem em Png</c:v>
-                      </c:pt>
-                      <c:pt idx="2">
-                        <c:v>Imagem em Tiff</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>Gaussiana 3x3</c:v>
-                      </c:pt>
-                      <c:pt idx="4">
-                        <c:v>Gaussiana 7x7</c:v>
-                      </c:pt>
-                      <c:pt idx="5">
-                        <c:v>Mediana 7x7</c:v>
-                      </c:pt>
-                      <c:pt idx="6">
-                        <c:v>Mediana 3x3</c:v>
-                      </c:pt>
-                      <c:pt idx="7">
-                        <c:v>Média 3x3</c:v>
-                      </c:pt>
-                      <c:pt idx="8">
-                        <c:v>Média 7x7</c:v>
-                      </c:pt>
-                      <c:pt idx="9">
-                        <c:v>Pouca alteração</c:v>
-                      </c:pt>
-                      <c:pt idx="10">
-                        <c:v>Adição de Texto</c:v>
-                      </c:pt>
-                      <c:pt idx="11">
-                        <c:v>Escala de Cinza</c:v>
-                      </c:pt>
-                      <c:pt idx="12">
-                        <c:v>Ruído Sal e Pimenta</c:v>
-                      </c:pt>
-                      <c:pt idx="13">
-                        <c:v>Bordas Enfatizadas</c:v>
-                      </c:pt>
-                      <c:pt idx="14">
-                        <c:v>Muita alteração</c:v>
-                      </c:pt>
-                      <c:pt idx="15">
-                        <c:v>Binarização com OTSU</c:v>
-                      </c:pt>
-                      <c:pt idx="16">
-                        <c:v>Metade Alterada</c:v>
-                      </c:pt>
-                      <c:pt idx="17">
-                        <c:v>Efeito Espelho</c:v>
-                      </c:pt>
-                      <c:pt idx="18">
-                        <c:v>Adição de Objetos</c:v>
-                      </c:pt>
-                    </c:strCache>
-                  </c:strRef>
-                </c:cat>
-                <c:val>
-                  <c:numRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:fullRef>
-                          <c15:sqref>LennaDatabase!#REF!</c15:sqref>
-                        </c15:fullRef>
-                        <c15:formulaRef>
-                          <c15:sqref>LennaDatabase!#REF!</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:numCache>
-                      <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="0"/>
-                    </c:numCache>
-                  </c:numRef>
-                </c:val>
-                <c:smooth val="0"/>
-                <c:extLst>
-                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                    <c16:uniqueId val="{00000004-955C-4A62-A711-ABC0A9DA8470}"/>
-                  </c:ext>
-                </c:extLst>
-              </c15:ser>
-            </c15:filteredLineSeries>
-          </c:ext>
-        </c:extLst>
+        <c:extLst/>
       </c:lineChart>
       <c:catAx>
         <c:axId val="392150687"/>
@@ -1575,7 +1557,10 @@
                   <a:defRPr/>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="pt-BR"/>
+                  <a:rPr lang="pt-BR" sz="1200">
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:rPr>
                   <a:t>Imagens Alteradas</a:t>
                 </a:r>
               </a:p>
@@ -1585,8 +1570,8 @@
             <c:manualLayout>
               <c:xMode val="edge"/>
               <c:yMode val="edge"/>
-              <c:x val="0.47140303978943293"/>
-              <c:y val="0.89287472538045831"/>
+              <c:x val="0.45126140863683328"/>
+              <c:y val="0.84322443641215805"/>
             </c:manualLayout>
           </c:layout>
           <c:overlay val="0"/>
@@ -1613,16 +1598,16 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="pt-BR"/>
@@ -1665,17 +1650,29 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr/>
+                  <a:defRPr sz="1200">
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="pt-BR"/>
+                  <a:rPr lang="pt-BR" sz="1200">
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:rPr>
                   <a:t>Distância</a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="pt-BR" baseline="0"/>
+                  <a:rPr lang="pt-BR" sz="1200" baseline="0">
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:rPr>
                   <a:t> de Hamming</a:t>
                 </a:r>
-                <a:endParaRPr lang="pt-BR"/>
+                <a:endParaRPr lang="pt-BR" sz="1200">
+                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                </a:endParaRPr>
               </a:p>
             </c:rich>
           </c:tx>
@@ -1683,8 +1680,8 @@
             <c:manualLayout>
               <c:xMode val="edge"/>
               <c:yMode val="edge"/>
-              <c:x val="1.9946221881624392E-2"/>
-              <c:y val="0.32089614169566544"/>
+              <c:x val="2.5246619874930071E-2"/>
+              <c:y val="0.29557958736170636"/>
             </c:manualLayout>
           </c:layout>
           <c:overlay val="0"/>
@@ -1733,8 +1730,8 @@
         <c:manualLayout>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="8.5704766815327571E-2"/>
-          <c:y val="0.94176582369826323"/>
+          <c:x val="8.4644652191311343E-2"/>
+          <c:y val="0.89987673581800842"/>
           <c:w val="0.82859036688846588"/>
           <c:h val="5.8234176301736718E-2"/>
         </c:manualLayout>
@@ -1752,16 +1749,16 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1100" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
                   <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
             </a:defRPr>
           </a:pPr>
           <a:endParaRPr lang="pt-BR"/>
@@ -1807,25 +1804,15 @@
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="0" vert="horz"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
+              <a:defRPr sz="1400"/>
             </a:pPr>
             <a:r>
-              <a:rPr lang="pt-BR" b="1"/>
-              <a:t>Distância de Hamming para Cada Algoritmo de Hashing entre a Imagem Original e uma Imagem Alterada</a:t>
+              <a:rPr lang="pt-BR" sz="1400"/>
+              <a:t>Distância de Hamming - Washington Database</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -1846,10 +1833,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="6.708286735947222E-2"/>
+          <c:x val="8.5098331998574014E-2"/>
           <c:y val="9.442161516380955E-2"/>
-          <c:w val="0.92001075377594732"/>
-          <c:h val="0.76399145860502204"/>
+          <c:w val="0.90199524132368758"/>
+          <c:h val="0.67714939908827187"/>
         </c:manualLayout>
       </c:layout>
       <c:lineChart>
@@ -2204,6 +2191,82 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000003-BAA3-4122-B737-7C7E68BA4B58}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="10"/>
+          <c:order val="4"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>WashingtonDatabase!#REF!</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>#REF!</c:v>
+                </c:pt>
+              </c:strCache>
+              <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
+            </c:strRef>
+          </c:tx>
+          <c:marker>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent6"/>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:schemeClr val="accent6"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:cat>
+            <c:strRef>
+              <c:extLst>
+                <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                  <c15:fullRef>
+                    <c15:sqref>WashingtonDatabase!$A$2:$A$8</c15:sqref>
+                  </c15:fullRef>
+                </c:ext>
+              </c:extLst>
+              <c:f>WashingtonDatabase!$A$3:$A$8</c:f>
+              <c:strCache>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>Fig01_WashingtonDC_Band1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Fig02_WashingtonDC_Band2</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Fig03_WashingtonDC_Band3</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Fig04_WashingtonDC_Band4</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Fig05_WashingtonDC_Band5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>Fig06_WashingtonDC_Band6</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>Fig07_WashingtonDC_Band7</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>WashingtonDatabase!#REF!</c:f>
+              <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart"/>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-BAA3-4122-B737-7C7E68BA4B58}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2326,104 +2389,7 @@
         <c:smooth val="0"/>
         <c:axId val="392150687"/>
         <c:axId val="392152351"/>
-        <c:extLst>
-          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-            <c15:filteredLineSeries>
-              <c15:ser>
-                <c:idx val="10"/>
-                <c:order val="4"/>
-                <c:tx>
-                  <c:strRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>WashingtonDatabase!#REF!</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:strCache>
-                      <c:ptCount val="1"/>
-                      <c:pt idx="0">
-                        <c:v>#REF!</c:v>
-                      </c:pt>
-                    </c:strCache>
-                  </c:strRef>
-                </c:tx>
-                <c:marker>
-                  <c:spPr>
-                    <a:solidFill>
-                      <a:schemeClr val="accent6"/>
-                    </a:solidFill>
-                    <a:ln>
-                      <a:solidFill>
-                        <a:schemeClr val="accent6"/>
-                      </a:solidFill>
-                    </a:ln>
-                  </c:spPr>
-                </c:marker>
-                <c:cat>
-                  <c:strRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:fullRef>
-                          <c15:sqref>WashingtonDatabase!$A$2:$A$8</c15:sqref>
-                        </c15:fullRef>
-                        <c15:formulaRef>
-                          <c15:sqref>WashingtonDatabase!$A$3:$A$8</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:strCache>
-                      <c:ptCount val="6"/>
-                      <c:pt idx="0">
-                        <c:v>Fig02_WashingtonDC_Band2</c:v>
-                      </c:pt>
-                      <c:pt idx="1">
-                        <c:v>Fig03_WashingtonDC_Band3</c:v>
-                      </c:pt>
-                      <c:pt idx="2">
-                        <c:v>Fig04_WashingtonDC_Band4</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>Fig05_WashingtonDC_Band5</c:v>
-                      </c:pt>
-                      <c:pt idx="4">
-                        <c:v>Fig06_WashingtonDC_Band6</c:v>
-                      </c:pt>
-                      <c:pt idx="5">
-                        <c:v>Fig07_WashingtonDC_Band7</c:v>
-                      </c:pt>
-                    </c:strCache>
-                  </c:strRef>
-                </c:cat>
-                <c:val>
-                  <c:numRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:fullRef>
-                          <c15:sqref>WashingtonDatabase!#REF!</c15:sqref>
-                        </c15:fullRef>
-                        <c15:formulaRef>
-                          <c15:sqref>WashingtonDatabase!#REF!</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:numCache>
-                      <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="0"/>
-                    </c:numCache>
-                  </c:numRef>
-                </c:val>
-                <c:smooth val="0"/>
-                <c:extLst>
-                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                    <c16:uniqueId val="{00000004-BAA3-4122-B737-7C7E68BA4B58}"/>
-                  </c:ext>
-                </c:extLst>
-              </c15:ser>
-            </c15:filteredLineSeries>
-          </c:ext>
-        </c:extLst>
+        <c:extLst/>
       </c:lineChart>
       <c:catAx>
         <c:axId val="392150687"/>
@@ -2439,10 +2405,10 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr/>
+                  <a:defRPr sz="1200"/>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="pt-BR"/>
+                  <a:rPr lang="pt-BR" sz="1200"/>
                   <a:t>Imagens Alteradas</a:t>
                 </a:r>
               </a:p>
@@ -2452,8 +2418,8 @@
             <c:manualLayout>
               <c:xMode val="edge"/>
               <c:yMode val="edge"/>
-              <c:x val="0.45844601967524629"/>
-              <c:y val="0.89885429396178429"/>
+              <c:x val="0.45281614712124196"/>
+              <c:y val="0.88043327807708249"/>
             </c:manualLayout>
           </c:layout>
           <c:overlay val="0"/>
@@ -2476,21 +2442,11 @@
           <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="-60000000" vert="horz"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
+              <a:defRPr/>
             </a:pPr>
             <a:endParaRPr lang="pt-BR"/>
           </a:p>
@@ -2532,17 +2488,12 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr/>
+                  <a:defRPr sz="1200"/>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="pt-BR"/>
-                  <a:t>Distância</a:t>
+                  <a:rPr lang="pt-BR" sz="1200"/>
+                  <a:t>Distância de Hamming</a:t>
                 </a:r>
-                <a:r>
-                  <a:rPr lang="pt-BR" baseline="0"/>
-                  <a:t> de Hamming</a:t>
-                </a:r>
-                <a:endParaRPr lang="pt-BR"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -2550,8 +2501,8 @@
             <c:manualLayout>
               <c:xMode val="edge"/>
               <c:yMode val="edge"/>
-              <c:x val="1.9946221881624392E-2"/>
-              <c:y val="0.32089614169566544"/>
+              <c:x val="2.1072174794158481E-2"/>
+              <c:y val="0.29458039784500623"/>
             </c:manualLayout>
           </c:layout>
           <c:overlay val="0"/>
@@ -2568,21 +2519,11 @@
           <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="-60000000" vert="horz"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
+              <a:defRPr/>
             </a:pPr>
             <a:endParaRPr lang="pt-BR"/>
           </a:p>
@@ -2590,7 +2531,7 @@
         <c:crossAx val="392150687"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
-        <c:majorUnit val="1"/>
+        <c:majorUnit val="2"/>
       </c:valAx>
     </c:plotArea>
     <c:legend>
@@ -2614,21 +2555,11 @@
         <a:effectLst/>
       </c:spPr>
       <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:bodyPr rot="0" vert="horz"/>
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
+            <a:defRPr/>
           </a:pPr>
           <a:endParaRPr lang="pt-BR"/>
         </a:p>
@@ -2643,7 +2574,10 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr>
+          <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+          <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+        </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="pt-BR"/>
     </a:p>
@@ -3461,25 +3395,15 @@
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="0" vert="horz"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
+              <a:defRPr sz="1400"/>
             </a:pPr>
             <a:r>
-              <a:rPr lang="pt-BR" b="1"/>
-              <a:t>Distância de Hamming para Cada Algoritmo de Hashing entre a Imagem Original e uma Imagem Alterada</a:t>
+              <a:rPr lang="pt-BR" sz="1400"/>
+              <a:t>Distância de Hamming - Park Database</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -3500,9 +3424,9 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="6.708286735947222E-2"/>
+          <c:x val="8.5401727096666075E-2"/>
           <c:y val="9.442161516380955E-2"/>
-          <c:w val="0.92001075377594732"/>
+          <c:w val="0.90169192685187738"/>
           <c:h val="0.67973668596353376"/>
         </c:manualLayout>
       </c:layout>
@@ -3898,89 +3822,6 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000003-9C5F-4C05-BDE1-43E87E9AEB94}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="10"/>
-          <c:order val="4"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>ParkDatabase!#REF!</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>#REF!</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:marker>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-              <a:ln>
-                <a:solidFill>
-                  <a:schemeClr val="accent6"/>
-                </a:solidFill>
-              </a:ln>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>ParkDatabase!$A$3:$A$12</c:f>
-              <c:strCache>
-                <c:ptCount val="10"/>
-                <c:pt idx="0">
-                  <c:v>Alternative (1)</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Alternative (2)</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Alternative (3)</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Alternative (4)</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Alternative (5)</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Alternative (6)</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Alternative (7)</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Alternative (8)</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Alternative (9)</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>Alternative (10)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>ParkDatabase!#REF!</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-9C5F-4C05-BDE1-43E87E9AEB94}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4113,7 +3954,113 @@
         <c:smooth val="0"/>
         <c:axId val="392150687"/>
         <c:axId val="392152351"/>
-        <c:extLst/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="10"/>
+                <c:order val="4"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>ParkDatabase!#REF!</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>#REF!</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:marker>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent6"/>
+                    </a:solidFill>
+                    <a:ln>
+                      <a:solidFill>
+                        <a:schemeClr val="accent6"/>
+                      </a:solidFill>
+                    </a:ln>
+                  </c:spPr>
+                </c:marker>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>ParkDatabase!$A$3:$A$12</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="10"/>
+                      <c:pt idx="0">
+                        <c:v>Alternative (1)</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>Alternative (2)</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>Alternative (3)</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>Alternative (4)</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>Alternative (5)</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>Alternative (6)</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>Alternative (7)</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>Alternative (8)</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>Alternative (9)</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>Alternative (10)</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>ParkDatabase!#REF!</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>1</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000004-9C5F-4C05-BDE1-43E87E9AEB94}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+          </c:ext>
+        </c:extLst>
       </c:lineChart>
       <c:catAx>
         <c:axId val="392150687"/>
@@ -4129,10 +4076,10 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr/>
+                  <a:defRPr sz="1200"/>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="pt-BR"/>
+                  <a:rPr lang="pt-BR" sz="1200"/>
                   <a:t>Imagens Alteradas</a:t>
                 </a:r>
               </a:p>
@@ -4142,8 +4089,8 @@
             <c:manualLayout>
               <c:xMode val="edge"/>
               <c:yMode val="edge"/>
-              <c:x val="0.46941254872126892"/>
-              <c:y val="0.90560344136371651"/>
+              <c:x val="0.45109372182755758"/>
+              <c:y val="0.89032898218380663"/>
             </c:manualLayout>
           </c:layout>
           <c:overlay val="0"/>
@@ -4166,21 +4113,11 @@
           <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="-60000000" vert="horz"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
+              <a:defRPr/>
             </a:pPr>
             <a:endParaRPr lang="pt-BR"/>
           </a:p>
@@ -4221,17 +4158,12 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr/>
+                  <a:defRPr sz="1200"/>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="pt-BR"/>
-                  <a:t>Distância</a:t>
+                  <a:rPr lang="pt-BR" sz="1200"/>
+                  <a:t>Distância de Hamming </a:t>
                 </a:r>
-                <a:r>
-                  <a:rPr lang="pt-BR" baseline="0"/>
-                  <a:t> de Hamming </a:t>
-                </a:r>
-                <a:endParaRPr lang="pt-BR"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -4239,8 +4171,8 @@
             <c:manualLayout>
               <c:xMode val="edge"/>
               <c:yMode val="edge"/>
-              <c:x val="1.9946221881624392E-2"/>
-              <c:y val="0.32089614169566544"/>
+              <c:x val="2.6411724402717707E-2"/>
+              <c:y val="0.31835039849901375"/>
             </c:manualLayout>
           </c:layout>
           <c:overlay val="0"/>
@@ -4257,21 +4189,11 @@
           <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="-60000000" vert="horz"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
+              <a:defRPr/>
             </a:pPr>
             <a:endParaRPr lang="pt-BR"/>
           </a:p>
@@ -4303,21 +4225,11 @@
         <a:effectLst/>
       </c:spPr>
       <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:bodyPr rot="0" vert="horz"/>
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
+            <a:defRPr/>
           </a:pPr>
           <a:endParaRPr lang="pt-BR"/>
         </a:p>
@@ -4332,7 +4244,10 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr>
+          <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+          <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+        </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="pt-BR"/>
     </a:p>
@@ -6066,14 +5981,17 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:rPr lang="pt-BR" b="1"/>
-              <a:t>Distância de Hamming para Cada Algoritmo de Hashing entre a Imagem Original e uma Imagem Alterada</a:t>
+              <a:rPr lang="pt-BR" b="1">
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+              </a:rPr>
+              <a:t>Distância de Hamming - Mountain Database</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -6094,10 +6012,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="6.708286735947222E-2"/>
+          <c:x val="9.2940197416589862E-2"/>
           <c:y val="9.442161516380955E-2"/>
-          <c:w val="0.92001075377594732"/>
-          <c:h val="0.67973668596353376"/>
+          <c:w val="0.89415346308483978"/>
+          <c:h val="0.64409628121041074"/>
         </c:manualLayout>
       </c:layout>
       <c:lineChart>
@@ -6948,146 +6866,6 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000003-81B7-4707-84D8-6D04D5AC34BE}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="10"/>
-          <c:order val="4"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>MountainDatabase!#REF!</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>#REF!</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:marker>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-              <a:ln>
-                <a:solidFill>
-                  <a:schemeClr val="accent6"/>
-                </a:solidFill>
-              </a:ln>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>MountainDatabase!$A$3:$A$31</c:f>
-              <c:strCache>
-                <c:ptCount val="29"/>
-                <c:pt idx="0">
-                  <c:v>Alternative (1)</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Alternative (2)</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Alternative (3)</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Alternative (4)</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Alternative (5)</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Alternative (6)</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Alternative (7)</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Alternative (8)</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Alternative (9)</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>Alternative (10)</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>Alternative (11)</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>Alternative (12)</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>Alternative (13)</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>Alternative (14)</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>Alternative (15)</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>Alternative (16)</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>Alternative (17)</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>Alternative (18)</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>Alternative (19)</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>Alternative (20)</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>Alternative (21)</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>Alternative (22)</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>Alternative (23)</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>Alternative (24)</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>Alternative (25)</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>Alternative (26)</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>Alternative (27)</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>Alternative (28)</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>Alternative (29)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>MountainDatabase!#REF!</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-81B7-4707-84D8-6D04D5AC34BE}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -7334,7 +7112,170 @@
         <c:smooth val="0"/>
         <c:axId val="392150687"/>
         <c:axId val="392152351"/>
-        <c:extLst/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="10"/>
+                <c:order val="4"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>MountainDatabase!#REF!</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>#REF!</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:marker>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent6"/>
+                    </a:solidFill>
+                    <a:ln>
+                      <a:solidFill>
+                        <a:schemeClr val="accent6"/>
+                      </a:solidFill>
+                    </a:ln>
+                  </c:spPr>
+                </c:marker>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>MountainDatabase!$A$3:$A$31</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="29"/>
+                      <c:pt idx="0">
+                        <c:v>Alternative (1)</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>Alternative (2)</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>Alternative (3)</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>Alternative (4)</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>Alternative (5)</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>Alternative (6)</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>Alternative (7)</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>Alternative (8)</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>Alternative (9)</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>Alternative (10)</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>Alternative (11)</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>Alternative (12)</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>Alternative (13)</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>Alternative (14)</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>Alternative (15)</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>Alternative (16)</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>Alternative (17)</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>Alternative (18)</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>Alternative (19)</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>Alternative (20)</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>Alternative (21)</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>Alternative (22)</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>Alternative (23)</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>Alternative (24)</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>Alternative (25)</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>Alternative (26)</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>Alternative (27)</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>Alternative (28)</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>Alternative (29)</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>MountainDatabase!#REF!</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>1</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000005-81B7-4707-84D8-6D04D5AC34BE}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+          </c:ext>
+        </c:extLst>
       </c:lineChart>
       <c:catAx>
         <c:axId val="392150687"/>
@@ -7350,10 +7291,16 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr/>
+                  <a:defRPr sz="1100">
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="pt-BR"/>
+                  <a:rPr lang="pt-BR" sz="1100">
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:rPr>
                   <a:t>Imagens Alteradas</a:t>
                 </a:r>
               </a:p>
@@ -7363,8 +7310,8 @@
             <c:manualLayout>
               <c:xMode val="edge"/>
               <c:yMode val="edge"/>
-              <c:x val="0.46941254872126892"/>
-              <c:y val="0.90560344136371651"/>
+              <c:x val="0.46941257379752288"/>
+              <c:y val="0.89287472538045831"/>
             </c:manualLayout>
           </c:layout>
           <c:overlay val="0"/>
@@ -7391,16 +7338,16 @@
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:defRPr sz="1000" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
                 <a:solidFill>
                   <a:schemeClr val="tx1">
                     <a:lumMod val="65000"/>
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
+                <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
                 <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
+                <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               </a:defRPr>
             </a:pPr>
             <a:endParaRPr lang="pt-BR"/>
@@ -7442,17 +7389,29 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr/>
+                  <a:defRPr sz="1100">
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="pt-BR"/>
+                  <a:rPr lang="pt-BR" sz="1100">
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:rPr>
                   <a:t>Distância</a:t>
                 </a:r>
                 <a:r>
-                  <a:rPr lang="pt-BR" baseline="0"/>
+                  <a:rPr lang="pt-BR" sz="1100" baseline="0">
+                    <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                    <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  </a:rPr>
                   <a:t> de Hamming </a:t>
                 </a:r>
-                <a:endParaRPr lang="pt-BR"/>
+                <a:endParaRPr lang="pt-BR" sz="1100">
+                  <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                  <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+                </a:endParaRPr>
               </a:p>
             </c:rich>
           </c:tx>
@@ -7460,8 +7419,8 @@
             <c:manualLayout>
               <c:xMode val="edge"/>
               <c:yMode val="edge"/>
-              <c:x val="1.9946221881624392E-2"/>
-              <c:y val="0.32089614169566544"/>
+              <c:x val="2.7815844723098122E-2"/>
+              <c:y val="0.31835039849901375"/>
             </c:manualLayout>
           </c:layout>
           <c:overlay val="0"/>
@@ -7528,16 +7487,16 @@
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+            <a:defRPr sz="1050" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
               <a:solidFill>
                 <a:schemeClr val="tx1">
                   <a:lumMod val="65000"/>
                   <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
+              <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
               <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
+              <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
             </a:defRPr>
           </a:pPr>
           <a:endParaRPr lang="pt-BR"/>
@@ -8371,29 +8330,27 @@
     <c:title>
       <c:tx>
         <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="0" vert="horz"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="1400" b="1" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
+              <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:rPr lang="pt-BR" b="1"/>
-              <a:t>Distância de Hamming para Cada Algoritmo de Hashing entre a Imagem Original e uma Imagem Alterada</a:t>
+              <a:rPr lang="pt-BR"/>
+              <a:t>Distância de Hamming - Palace Database</a:t>
             </a:r>
           </a:p>
         </c:rich>
       </c:tx>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.36201194357355948"/>
+          <c:y val="1.583461513365288E-2"/>
+        </c:manualLayout>
+      </c:layout>
       <c:overlay val="0"/>
       <c:spPr>
         <a:noFill/>
@@ -8410,10 +8367,10 @@
           <c:layoutTarget val="inner"/>
           <c:xMode val="edge"/>
           <c:yMode val="edge"/>
-          <c:x val="6.708286735947222E-2"/>
+          <c:x val="8.3846554170794507E-2"/>
           <c:y val="9.442161516380955E-2"/>
-          <c:w val="0.92001075377594732"/>
-          <c:h val="0.67973668596353376"/>
+          <c:w val="0.90324708501182782"/>
+          <c:h val="0.61375903373105511"/>
         </c:manualLayout>
       </c:layout>
       <c:lineChart>
@@ -9264,146 +9221,6 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000003-94E7-4DDB-A195-CFD4F9D70B71}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="10"/>
-          <c:order val="4"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>PalaceDatabase!#REF!</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>#REF!</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:marker>
-            <c:spPr>
-              <a:solidFill>
-                <a:schemeClr val="accent6"/>
-              </a:solidFill>
-              <a:ln>
-                <a:solidFill>
-                  <a:schemeClr val="accent6"/>
-                </a:solidFill>
-              </a:ln>
-            </c:spPr>
-          </c:marker>
-          <c:cat>
-            <c:strRef>
-              <c:f>PalaceDatabase!$A$3:$A$31</c:f>
-              <c:strCache>
-                <c:ptCount val="29"/>
-                <c:pt idx="0">
-                  <c:v>Alternative (1)</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>Alternative (2)</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>Alternative (3)</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>Alternative (4)</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>Alternative (5)</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>Alternative (6)</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>Alternative (7)</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>Alternative (8)</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>Alternative (9)</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>Alternative (10)</c:v>
-                </c:pt>
-                <c:pt idx="10">
-                  <c:v>Alternative (11)</c:v>
-                </c:pt>
-                <c:pt idx="11">
-                  <c:v>Alternative (12)</c:v>
-                </c:pt>
-                <c:pt idx="12">
-                  <c:v>Alternative (13)</c:v>
-                </c:pt>
-                <c:pt idx="13">
-                  <c:v>Alternative (14)</c:v>
-                </c:pt>
-                <c:pt idx="14">
-                  <c:v>Alternative (15)</c:v>
-                </c:pt>
-                <c:pt idx="15">
-                  <c:v>Alternative (16)</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>Alternative (17)</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>Alternative (18)</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>Alternative (19)</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>Alternative (20)</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>Alternative (21)</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>Alternative (22)</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>Alternative (23)</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>Alternative (24)</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>Alternative (25)</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>Alternative (26)</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>Alternative (27)</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>Alternative (28)</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>Alternative (29)</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>PalaceDatabase!#REF!</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>1</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart">
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-94E7-4DDB-A195-CFD4F9D70B71}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -9650,7 +9467,170 @@
         <c:smooth val="0"/>
         <c:axId val="392150687"/>
         <c:axId val="392152351"/>
-        <c:extLst/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredLineSeries>
+              <c15:ser>
+                <c:idx val="10"/>
+                <c:order val="4"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>PalaceDatabase!#REF!</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>#REF!</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:marker>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent6"/>
+                    </a:solidFill>
+                    <a:ln>
+                      <a:solidFill>
+                        <a:schemeClr val="accent6"/>
+                      </a:solidFill>
+                    </a:ln>
+                  </c:spPr>
+                </c:marker>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>PalaceDatabase!$A$3:$A$31</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="29"/>
+                      <c:pt idx="0">
+                        <c:v>Alternative (1)</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>Alternative (2)</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>Alternative (3)</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>Alternative (4)</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>Alternative (5)</c:v>
+                      </c:pt>
+                      <c:pt idx="5">
+                        <c:v>Alternative (6)</c:v>
+                      </c:pt>
+                      <c:pt idx="6">
+                        <c:v>Alternative (7)</c:v>
+                      </c:pt>
+                      <c:pt idx="7">
+                        <c:v>Alternative (8)</c:v>
+                      </c:pt>
+                      <c:pt idx="8">
+                        <c:v>Alternative (9)</c:v>
+                      </c:pt>
+                      <c:pt idx="9">
+                        <c:v>Alternative (10)</c:v>
+                      </c:pt>
+                      <c:pt idx="10">
+                        <c:v>Alternative (11)</c:v>
+                      </c:pt>
+                      <c:pt idx="11">
+                        <c:v>Alternative (12)</c:v>
+                      </c:pt>
+                      <c:pt idx="12">
+                        <c:v>Alternative (13)</c:v>
+                      </c:pt>
+                      <c:pt idx="13">
+                        <c:v>Alternative (14)</c:v>
+                      </c:pt>
+                      <c:pt idx="14">
+                        <c:v>Alternative (15)</c:v>
+                      </c:pt>
+                      <c:pt idx="15">
+                        <c:v>Alternative (16)</c:v>
+                      </c:pt>
+                      <c:pt idx="16">
+                        <c:v>Alternative (17)</c:v>
+                      </c:pt>
+                      <c:pt idx="17">
+                        <c:v>Alternative (18)</c:v>
+                      </c:pt>
+                      <c:pt idx="18">
+                        <c:v>Alternative (19)</c:v>
+                      </c:pt>
+                      <c:pt idx="19">
+                        <c:v>Alternative (20)</c:v>
+                      </c:pt>
+                      <c:pt idx="20">
+                        <c:v>Alternative (21)</c:v>
+                      </c:pt>
+                      <c:pt idx="21">
+                        <c:v>Alternative (22)</c:v>
+                      </c:pt>
+                      <c:pt idx="22">
+                        <c:v>Alternative (23)</c:v>
+                      </c:pt>
+                      <c:pt idx="23">
+                        <c:v>Alternative (24)</c:v>
+                      </c:pt>
+                      <c:pt idx="24">
+                        <c:v>Alternative (25)</c:v>
+                      </c:pt>
+                      <c:pt idx="25">
+                        <c:v>Alternative (26)</c:v>
+                      </c:pt>
+                      <c:pt idx="26">
+                        <c:v>Alternative (27)</c:v>
+                      </c:pt>
+                      <c:pt idx="27">
+                        <c:v>Alternative (28)</c:v>
+                      </c:pt>
+                      <c:pt idx="28">
+                        <c:v>Alternative (29)</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>PalaceDatabase!#REF!</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>General</c:formatCode>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>1</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:smooth val="0"/>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000004-94E7-4DDB-A195-CFD4F9D70B71}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredLineSeries>
+          </c:ext>
+        </c:extLst>
       </c:lineChart>
       <c:catAx>
         <c:axId val="392150687"/>
@@ -9666,10 +9646,10 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr/>
+                  <a:defRPr sz="1400"/>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="pt-BR"/>
+                  <a:rPr lang="pt-BR" sz="1400"/>
                   <a:t>Imagens Alteradas</a:t>
                 </a:r>
               </a:p>
@@ -9679,8 +9659,8 @@
             <c:manualLayout>
               <c:xMode val="edge"/>
               <c:yMode val="edge"/>
-              <c:x val="0.46941254872126892"/>
-              <c:y val="0.90560344136371651"/>
+              <c:x val="0.45264889886828885"/>
+              <c:y val="0.87393422857786451"/>
             </c:manualLayout>
           </c:layout>
           <c:overlay val="0"/>
@@ -9703,21 +9683,11 @@
           <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="-60000000" vert="horz"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
+              <a:defRPr/>
             </a:pPr>
             <a:endParaRPr lang="pt-BR"/>
           </a:p>
@@ -9758,17 +9728,12 @@
               <a:lstStyle/>
               <a:p>
                 <a:pPr>
-                  <a:defRPr/>
+                  <a:defRPr sz="1200"/>
                 </a:pPr>
                 <a:r>
-                  <a:rPr lang="pt-BR"/>
-                  <a:t>Distância</a:t>
+                  <a:rPr lang="pt-BR" sz="1200"/>
+                  <a:t>Distância de Hamming </a:t>
                 </a:r>
-                <a:r>
-                  <a:rPr lang="pt-BR" baseline="0"/>
-                  <a:t> de Hamming </a:t>
-                </a:r>
-                <a:endParaRPr lang="pt-BR"/>
               </a:p>
             </c:rich>
           </c:tx>
@@ -9794,21 +9759,11 @@
           <a:effectLst/>
         </c:spPr>
         <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:bodyPr rot="-60000000" vert="horz"/>
           <a:lstStyle/>
           <a:p>
             <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
+              <a:defRPr/>
             </a:pPr>
             <a:endParaRPr lang="pt-BR"/>
           </a:p>
@@ -9840,21 +9795,11 @@
         <a:effectLst/>
       </c:spPr>
       <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:bodyPr rot="0" vert="horz"/>
         <a:lstStyle/>
         <a:p>
           <a:pPr>
-            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
+            <a:defRPr sz="1200"/>
           </a:pPr>
           <a:endParaRPr lang="pt-BR"/>
         </a:p>
@@ -9869,7 +9814,10 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr>
+          <a:latin typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+          <a:cs typeface="Times New Roman" panose="02020603050405020304" pitchFamily="18" charset="0"/>
+        </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="pt-BR"/>
     </a:p>
@@ -16242,8 +16190,8 @@
     <xdr:to>
       <xdr:col>12</xdr:col>
       <xdr:colOff>603250</xdr:colOff>
-      <xdr:row>48</xdr:row>
-      <xdr:rowOff>10583</xdr:rowOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>100853</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -16599,8 +16547,8 @@
     <xdr:to>
       <xdr:col>11</xdr:col>
       <xdr:colOff>592665</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>127000</xdr:rowOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>10583</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -18351,7 +18299,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.7109375" bestFit="1" customWidth="1"/>
@@ -19335,7 +19283,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="18.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="25" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="18.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="18.85546875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19.7109375" bestFit="1" customWidth="1"/>
